--- a/data/trans_dic/P20B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P20B-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que estuvo en lista de espera por ingreso hospitalario</t>
+          <t>Población que estuvo en lista de espera por ingreso hospitalario (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,48; 37,62</t>
+          <t>16,27; 37,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,24; 38,98</t>
+          <t>19,44; 38,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,44; 42,45</t>
+          <t>17,94; 42,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,02; 45,23</t>
+          <t>23,88; 46,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,78; 41,43</t>
+          <t>22,63; 41,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,15; 37,9</t>
+          <t>21,22; 38,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,3; 49,38</t>
+          <t>26,66; 48,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,14; 32,95</t>
+          <t>16,42; 34,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,44; 36,98</t>
+          <t>23,24; 36,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,15; 35,37</t>
+          <t>22,44; 34,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,47; 42,91</t>
+          <t>25,72; 42,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,17; 36,41</t>
+          <t>22,68; 36,51</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 35,7</t>
+          <t>11,54; 36,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,47; 42,43</t>
+          <t>23,04; 41,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,39; 53,54</t>
+          <t>30,42; 54,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,03; 44,19</t>
+          <t>26,14; 45,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 18,94</t>
+          <t>6,93; 18,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,17; 29,24</t>
+          <t>15,12; 28,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,49; 32,24</t>
+          <t>16,97; 31,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,95; 33,35</t>
+          <t>17,89; 32,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,86; 20,88</t>
+          <t>10,01; 21,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,4; 30,84</t>
+          <t>19,93; 31,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,31; 36,8</t>
+          <t>23,99; 36,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,07; 35,63</t>
+          <t>23,02; 35,47</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,99; 59,6</t>
+          <t>17,43; 60,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,89</t>
+          <t>0,0; 60,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 37,41</t>
+          <t>3,64; 37,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,44; 46,27</t>
+          <t>14,58; 47,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 27,91</t>
+          <t>2,96; 26,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,94; 37,61</t>
+          <t>10,76; 37,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,87</t>
+          <t>0,0; 15,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,57; 27,99</t>
+          <t>10,18; 27,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,61; 35,09</t>
+          <t>12,55; 35,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,15; 35,75</t>
+          <t>11,62; 36,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 17,56</t>
+          <t>3,36; 18,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,49; 33,45</t>
+          <t>15,39; 33,52</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,86; 34,1</t>
+          <t>19,5; 34,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,29; 37,26</t>
+          <t>23,33; 36,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,16; 40,84</t>
+          <t>25,74; 41,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,91; 40,21</t>
+          <t>26,87; 40,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,68; 25,34</t>
+          <t>14,8; 25,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,77; 29,43</t>
+          <t>19,95; 29,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,18; 29,62</t>
+          <t>18,85; 30,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,11; 28,85</t>
+          <t>18,33; 28,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,3; 26,69</t>
+          <t>18,71; 26,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,63; 30,25</t>
+          <t>22,68; 30,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,44; 32,62</t>
+          <t>23,71; 32,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,63; 31,93</t>
+          <t>23,85; 32,35</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que estuvo en lista de espera por ingreso hospitalario</t>
+          <t>Población que estuvo en lista de espera por ingreso hospitalario (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10894; 24867</t>
+          <t>10757; 24466</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19084; 38670</t>
+          <t>19281; 38039</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10214; 23514</t>
+          <t>9939; 23385</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12797; 25147</t>
+          <t>13279; 25575</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22888; 41617</t>
+          <t>22735; 41213</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28515; 51109</t>
+          <t>28613; 51505</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21671; 40687</t>
+          <t>21963; 40254</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9032; 18440</t>
+          <t>9186; 19101</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39036; 61590</t>
+          <t>38708; 60144</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54177; 82775</t>
+          <t>52524; 80741</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36474; 59121</t>
+          <t>35443; 58829</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24729; 40620</t>
+          <t>25306; 40728</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5335; 16076</t>
+          <t>5195; 16469</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22110; 39978</t>
+          <t>21707; 39167</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25458; 43422</t>
+          <t>24671; 43888</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23718; 41873</t>
+          <t>24774; 43150</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8027; 21598</t>
+          <t>7908; 21632</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24023; 46294</t>
+          <t>23932; 45084</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23356; 45657</t>
+          <t>24039; 45311</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20901; 38836</t>
+          <t>20836; 37997</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15678; 33217</t>
+          <t>15924; 33548</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51509; 77890</t>
+          <t>50325; 78546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54142; 81961</t>
+          <t>53425; 81328</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48734; 75260</t>
+          <t>48620; 74915</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4110; 13620</t>
+          <t>3982; 13758</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 8567</t>
+          <t>0; 8197</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>988; 9719</t>
+          <t>946; 9865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5712; 17116</t>
+          <t>5392; 17433</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1006; 9452</t>
+          <t>1003; 9051</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4528; 15560</t>
+          <t>4453; 15434</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6310</t>
+          <t>0; 7274</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4236; 12389</t>
+          <t>4506; 12113</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7149; 19901</t>
+          <t>7118; 20226</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6130; 19660</t>
+          <t>6391; 20241</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2134; 12553</t>
+          <t>2401; 13258</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11776; 27180</t>
+          <t>12505; 27234</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25274; 45688</t>
+          <t>26122; 45854</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48223; 77139</t>
+          <t>48295; 76402</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42502; 66360</t>
+          <t>41819; 67203</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50415; 75338</t>
+          <t>50345; 75286</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38941; 62932</t>
+          <t>36755; 62079</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66124; 98443</t>
+          <t>66734; 98841</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51703; 79847</t>
+          <t>50800; 81415</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39236; 62506</t>
+          <t>39711; 60877</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69951; 102057</t>
+          <t>71546; 102438</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>122549; 163842</t>
+          <t>122841; 165369</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>101246; 140920</t>
+          <t>102423; 142450</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>95483; 128996</t>
+          <t>96380; 130718</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P20B-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,27; 37,02</t>
+          <t>16,28; 37,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,44; 38,35</t>
+          <t>20,26; 38,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,94; 42,22</t>
+          <t>18,09; 42,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,88; 46,0</t>
+          <t>23,74; 45,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,63; 41,02</t>
+          <t>23,64; 40,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,22; 38,19</t>
+          <t>21,54; 37,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,66; 48,86</t>
+          <t>26,63; 48,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,42; 34,13</t>
+          <t>17,02; 34,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,24; 36,11</t>
+          <t>23,08; 37,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,44; 34,5</t>
+          <t>23,03; 35,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,72; 42,7</t>
+          <t>25,99; 41,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,68; 36,51</t>
+          <t>22,68; 36,62</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,54; 36,57</t>
+          <t>10,85; 34,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,04; 41,57</t>
+          <t>22,68; 43,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,42; 54,11</t>
+          <t>30,63; 52,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,14; 45,53</t>
+          <t>26,81; 45,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 18,97</t>
+          <t>7,2; 20,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,12; 28,48</t>
+          <t>15,63; 28,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,97; 31,99</t>
+          <t>17,21; 32,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,89; 32,63</t>
+          <t>17,23; 31,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,01; 21,09</t>
+          <t>9,93; 20,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,93; 31,1</t>
+          <t>19,77; 31,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23,99; 36,51</t>
+          <t>24,81; 36,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,02; 35,47</t>
+          <t>23,59; 35,26</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,43; 60,21</t>
+          <t>17,94; 61,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,18</t>
+          <t>0,0; 59,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 37,97</t>
+          <t>3,86; 38,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,58; 47,13</t>
+          <t>14,88; 44,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 26,72</t>
+          <t>2,96; 28,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,76; 37,3</t>
+          <t>9,97; 35,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,98</t>
+          <t>0,0; 15,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,18; 27,37</t>
+          <t>9,94; 29,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,55; 35,66</t>
+          <t>12,52; 36,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,62; 36,8</t>
+          <t>11,45; 35,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 18,55</t>
+          <t>2,87; 18,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,39; 33,52</t>
+          <t>15,33; 31,75</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,5; 34,22</t>
+          <t>19,75; 33,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,33; 36,9</t>
+          <t>22,72; 36,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,74; 41,36</t>
+          <t>26,65; 42,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,87; 40,18</t>
+          <t>27,37; 40,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,8; 25,0</t>
+          <t>15,55; 25,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,95; 29,55</t>
+          <t>20,11; 29,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 30,21</t>
+          <t>19,59; 30,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,33; 28,1</t>
+          <t>18,36; 28,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,71; 26,79</t>
+          <t>18,4; 26,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,68; 30,53</t>
+          <t>22,67; 30,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,71; 32,97</t>
+          <t>23,57; 32,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,85; 32,35</t>
+          <t>23,78; 32,4</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32242</t>
+          <t>34611</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10757; 24466</t>
+          <t>10761; 24973</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19281; 38039</t>
+          <t>20100; 38165</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9939; 23385</t>
+          <t>10019; 23710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13279; 25575</t>
+          <t>13828; 26406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22735; 41213</t>
+          <t>23747; 40829</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28613; 51505</t>
+          <t>29041; 50285</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21963; 40254</t>
+          <t>21940; 40168</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9186; 19101</t>
+          <t>10294; 21061</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38708; 60144</t>
+          <t>38442; 61653</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52524; 80741</t>
+          <t>53891; 82767</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35443; 58829</t>
+          <t>35808; 57853</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25306; 40728</t>
+          <t>26932; 43475</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>69798</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5195; 16469</t>
+          <t>4885; 15689</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21707; 39167</t>
+          <t>21368; 40518</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24671; 43888</t>
+          <t>24839; 42611</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24774; 43150</t>
+          <t>28310; 48433</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7908; 21632</t>
+          <t>8216; 23074</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23932; 45084</t>
+          <t>24744; 45403</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24039; 45311</t>
+          <t>24372; 45440</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20836; 37997</t>
+          <t>23194; 42542</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15924; 33548</t>
+          <t>15800; 32321</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50325; 78546</t>
+          <t>49923; 78802</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53425; 81328</t>
+          <t>55256; 82183</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48620; 74915</t>
+          <t>56660; 84705</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>20523</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3982; 13758</t>
+          <t>4098; 13947</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 8197</t>
+          <t>0; 8160</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>946; 9865</t>
+          <t>1003; 10030</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5392; 17433</t>
+          <t>6025; 18057</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1003; 9051</t>
+          <t>1002; 9801</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4453; 15434</t>
+          <t>4124; 14843</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7274</t>
+          <t>0; 6865</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4506; 12113</t>
+          <t>4951; 14584</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7118; 20226</t>
+          <t>7103; 20818</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6391; 20241</t>
+          <t>6298; 19476</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2401; 13258</t>
+          <t>2048; 13184</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12505; 27234</t>
+          <t>13842; 28662</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>49677</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>111954</t>
+          <t>124932</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26122; 45854</t>
+          <t>26457; 45426</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48295; 76402</t>
+          <t>47032; 74903</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41819; 67203</t>
+          <t>43294; 68491</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50345; 75286</t>
+          <t>55924; 82413</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36755; 62079</t>
+          <t>38624; 63528</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66734; 98841</t>
+          <t>67275; 99595</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50800; 81415</t>
+          <t>52809; 81571</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39711; 60877</t>
+          <t>44976; 69364</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71546; 102438</t>
+          <t>70362; 102503</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>122841; 165369</t>
+          <t>122778; 162727</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102423; 142450</t>
+          <t>101805; 140282</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>96380; 130718</t>
+          <t>106826; 145543</t>
         </is>
       </c>
     </row>
